--- a/erp-server/erp-server-dmp/src/main/resources/excel/platformInitStockError.xlsx
+++ b/erp-server/erp-server-dmp/src/main/resources/excel/platformInitStockError.xlsx
@@ -27,9 +27,31 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>核对仓库</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -45,6 +67,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -104,6 +133,9 @@
   </si>
   <si>
     <t>错误信息</t>
+  </si>
+  <si>
+    <t>{.sourceSystemName}</t>
   </si>
   <si>
     <t>{.checkMonth}</t>
@@ -1087,24 +1119,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="18.25" customWidth="1"/>
-    <col min="2" max="2" width="13.3666666666667" customWidth="1"/>
-    <col min="3" max="3" width="27.125" customWidth="1"/>
-    <col min="4" max="4" width="13.3666666666667" customWidth="1"/>
-    <col min="5" max="5" width="18.375" customWidth="1"/>
+    <col min="1" max="1" width="21.5" customWidth="1"/>
+    <col min="2" max="2" width="18.25" customWidth="1"/>
+    <col min="3" max="3" width="13.3666666666667" customWidth="1"/>
+    <col min="4" max="4" width="27.125" customWidth="1"/>
+    <col min="5" max="5" width="13.3666666666667" customWidth="1"/>
+    <col min="6" max="6" width="18.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:5">
+    <row r="1" ht="14.25" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -1113,22 +1146,28 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
